--- a/rockphypy-main/data/Jorlin/fracture_sensitivity.xlsx
+++ b/rockphypy-main/data/Jorlin/fracture_sensitivity.xlsx
@@ -499,34 +499,34 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D2" t="n">
-        <v>293.0985075382</v>
+        <v>492.1705119600307</v>
       </c>
       <c r="E2" t="n">
-        <v>199.595107021608</v>
+        <v>245.7991865496309</v>
       </c>
       <c r="F2" t="n">
-        <v>6.874168604799863</v>
+        <v>365.3762061097156</v>
       </c>
       <c r="G2" t="n">
-        <v>-106.1869554804285</v>
+        <v>55.12932017266317</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04203200961438115</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.2335187511355457</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05119217987267394</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.3241131532540648</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02254269985023937</v>
+        <v>0.631858442587526</v>
       </c>
     </row>
     <row r="3">
@@ -537,34 +537,34 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D3" t="n">
-        <v>293.0985075382</v>
+        <v>492.1705119600307</v>
       </c>
       <c r="E3" t="n">
-        <v>199.595107021608</v>
+        <v>245.7991865496309</v>
       </c>
       <c r="F3" t="n">
-        <v>6.874168604799863</v>
+        <v>365.3762061097156</v>
       </c>
       <c r="G3" t="n">
-        <v>-106.1869554804285</v>
+        <v>55.12932017266317</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04203200961438115</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.2335187511355457</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05119217987267394</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.3241131532540648</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02254269985023937</v>
+        <v>0.631858442587526</v>
       </c>
     </row>
     <row r="4">
@@ -575,34 +575,34 @@
         <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D4" t="n">
-        <v>293.0985075382</v>
+        <v>492.1705119600307</v>
       </c>
       <c r="E4" t="n">
-        <v>199.595107021608</v>
+        <v>245.7991865496309</v>
       </c>
       <c r="F4" t="n">
-        <v>6.874168604799863</v>
+        <v>365.3762061097156</v>
       </c>
       <c r="G4" t="n">
-        <v>-106.1869554804285</v>
+        <v>55.12932017266317</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04203200961438115</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.2335187511355457</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05119217987267394</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.3241131532540648</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02254269985023937</v>
+        <v>0.631858442587526</v>
       </c>
     </row>
     <row r="5">
@@ -613,34 +613,34 @@
         <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D5" t="n">
-        <v>293.0985075382</v>
+        <v>492.1705119600307</v>
       </c>
       <c r="E5" t="n">
-        <v>199.595107021608</v>
+        <v>245.7991865496309</v>
       </c>
       <c r="F5" t="n">
-        <v>6.874168604799863</v>
+        <v>365.3762061097156</v>
       </c>
       <c r="G5" t="n">
-        <v>-106.1869554804285</v>
+        <v>55.12932017266317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04203200961438115</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.2335187511355457</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05119217987267394</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.3241131532540648</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02254269985023937</v>
+        <v>0.631858442587526</v>
       </c>
     </row>
     <row r="6">
@@ -651,34 +651,34 @@
         <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D6" t="n">
-        <v>293.0985075382</v>
+        <v>492.1705119600307</v>
       </c>
       <c r="E6" t="n">
-        <v>199.595107021608</v>
+        <v>245.7991865496309</v>
       </c>
       <c r="F6" t="n">
-        <v>6.874168604799863</v>
+        <v>365.3762061097156</v>
       </c>
       <c r="G6" t="n">
-        <v>-106.1869554804285</v>
+        <v>55.12932017266317</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04203200961438115</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.2335187511355457</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05119217987267394</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.3241131532540648</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02254269985023937</v>
+        <v>0.631858442587526</v>
       </c>
     </row>
     <row r="7">
@@ -689,34 +689,34 @@
         <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D7" t="n">
-        <v>293.0985075382</v>
+        <v>492.1705119600307</v>
       </c>
       <c r="E7" t="n">
-        <v>199.595107021608</v>
+        <v>245.7991865496309</v>
       </c>
       <c r="F7" t="n">
-        <v>6.874168604799863</v>
+        <v>365.3762061097156</v>
       </c>
       <c r="G7" t="n">
-        <v>-106.1869554804285</v>
+        <v>55.12932017266317</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04203200961438115</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.2335187511355457</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05119217987267394</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.3241131532540648</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02254269985023937</v>
+        <v>0.631858442587526</v>
       </c>
     </row>
     <row r="8">
@@ -727,34 +727,34 @@
         <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D8" t="n">
-        <v>293.0985075382</v>
+        <v>492.1705119600307</v>
       </c>
       <c r="E8" t="n">
-        <v>199.595107021608</v>
+        <v>245.7991865496309</v>
       </c>
       <c r="F8" t="n">
-        <v>6.874168604799863</v>
+        <v>365.3762061097156</v>
       </c>
       <c r="G8" t="n">
-        <v>-106.1869554804285</v>
+        <v>55.12932017266317</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04203200961438115</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.2335187511355457</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05119217987267394</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.3241131532540648</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02254269985023937</v>
+        <v>0.631858442587526</v>
       </c>
     </row>
     <row r="9">
@@ -765,34 +765,34 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D9" t="n">
-        <v>292.5826977380374</v>
+        <v>484.5973889494016</v>
       </c>
       <c r="E9" t="n">
-        <v>209.2106852051356</v>
+        <v>240.5227343174773</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1569643920922014</v>
+        <v>356.0699003038171</v>
       </c>
       <c r="G9" t="n">
-        <v>-124.9444755208731</v>
+        <v>33.91468195246738</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02057072876766438</v>
+        <v>0.9350953728995025</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06724604571927491</v>
+        <v>0.1205505410440971</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.9433022757167578</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0946978016536484</v>
+        <v>0.1981573302063242</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04505522510458784</v>
+        <v>0.5421252389683803</v>
       </c>
     </row>
     <row r="10">
@@ -803,34 +803,34 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D10" t="n">
-        <v>292.5247335200071</v>
+        <v>482.9479667196835</v>
       </c>
       <c r="E10" t="n">
-        <v>207.6575221392891</v>
+        <v>241.1867878602329</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.119562432887359</v>
+        <v>353.9332535909922</v>
       </c>
       <c r="G10" t="n">
-        <v>-122.0934945216912</v>
+        <v>37.10738835340337</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01815901351561273</v>
+        <v>0.9209591790728781</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0563840806307558</v>
+        <v>0.1347678478308145</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01495706677073683</v>
+        <v>0.9302849723161258</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08030455390038869</v>
+        <v>0.2171131077362401</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04072463482731043</v>
+        <v>0.5431420223099584</v>
       </c>
     </row>
     <row r="11">
@@ -841,34 +841,34 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D11" t="n">
-        <v>292.4619191098761</v>
+        <v>479.9662398690272</v>
       </c>
       <c r="E11" t="n">
-        <v>204.4068364928337</v>
+        <v>242.7608883348439</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.766069856404998</v>
+        <v>350.0345679833634</v>
       </c>
       <c r="G11" t="n">
-        <v>-115.945874417519</v>
+        <v>43.99709555133483</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01554549648546373</v>
+        <v>0.8954046133955784</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03365057969838291</v>
+        <v>0.1684691503911377</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04274729884059217</v>
+        <v>0.9065326256536853</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0492681424765103</v>
+        <v>0.2580187659740166</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03173459894746596</v>
+        <v>0.5487164865335223</v>
       </c>
     </row>
     <row r="12">
@@ -879,34 +879,34 @@
         <v>45</v>
       </c>
       <c r="C12" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D12" t="n">
-        <v>292.4867284690106</v>
+        <v>479.4748744829643</v>
       </c>
       <c r="E12" t="n">
-        <v>202.0945901496015</v>
+        <v>244.057786012336</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.678056205785123</v>
+        <v>349.3072867772419</v>
       </c>
       <c r="G12" t="n">
-        <v>-111.3969621094126</v>
+        <v>49.11049290990471</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01657773864884683</v>
+        <v>0.8911934197958251</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01748000520525553</v>
+        <v>0.1962355742782414</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04969759657764303</v>
+        <v>0.9021017386657547</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02630284671438023</v>
+        <v>0.2883780945745714</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02401932183337133</v>
+        <v>0.5608896368980766</v>
       </c>
     </row>
     <row r="13">
@@ -917,34 +917,34 @@
         <v>60</v>
       </c>
       <c r="C13" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D13" t="n">
-        <v>292.6137025687393</v>
+        <v>483.114767514979</v>
       </c>
       <c r="E13" t="n">
-        <v>202.0374786696764</v>
+        <v>244.1236783031266</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.88892143358464</v>
+        <v>353.8912935562262</v>
       </c>
       <c r="G13" t="n">
-        <v>-111.2619255046742</v>
+        <v>49.29484250371166</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02186074570624712</v>
+        <v>0.9223887271474996</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01708059904196139</v>
+        <v>0.1976463203291735</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02082039370009335</v>
+        <v>0.930029335059872</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02562111109133765</v>
+        <v>0.2894726173552788</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02072069904797467</v>
+        <v>0.5765953412280829</v>
       </c>
     </row>
     <row r="14">
@@ -955,34 +955,34 @@
         <v>75</v>
       </c>
       <c r="C14" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D14" t="n">
-        <v>292.8698008747846</v>
+        <v>488.4214859959404</v>
       </c>
       <c r="E14" t="n">
-        <v>203.4119277255755</v>
+        <v>243.3751085039278</v>
       </c>
       <c r="F14" t="n">
-        <v>2.856385714526128</v>
+        <v>360.6032195351815</v>
       </c>
       <c r="G14" t="n">
-        <v>-113.9594119680078</v>
+        <v>46.30721128800113</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0325162192328775</v>
+        <v>0.9678693807234022</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02669273700056475</v>
+        <v>0.1816195306183375</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0205724372096268</v>
+        <v>0.9709210633676976</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03923943790199182</v>
+        <v>0.2717344148541537</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02970496459641719</v>
+        <v>0.590272216817555</v>
       </c>
     </row>
     <row r="15">
@@ -993,34 +993,34 @@
         <v>90</v>
       </c>
       <c r="C15" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D15" t="n">
-        <v>293.0283466353986</v>
+        <v>490.9289147388607</v>
       </c>
       <c r="E15" t="n">
-        <v>204.2278745738961</v>
+        <v>242.9485325906317</v>
       </c>
       <c r="F15" t="n">
-        <v>5.584496552556057</v>
+        <v>363.7659143853179</v>
       </c>
       <c r="G15" t="n">
-        <v>-115.5397076114234</v>
+        <v>44.55157664160744</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03911282731306558</v>
+        <v>0.9893590260535915</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0323990188298434</v>
+        <v>0.1724865914249283</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04136351878323943</v>
+        <v>0.9901894609837968</v>
       </c>
       <c r="K15" t="n">
-        <v>0.04721759935785705</v>
+        <v>0.2613108382386857</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03860080173781907</v>
+        <v>0.595865255696587</v>
       </c>
     </row>
     <row r="16">
@@ -1031,34 +1031,34 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D16" t="n">
-        <v>292.2453247083276</v>
+        <v>477.073426267784</v>
       </c>
       <c r="E16" t="n">
-        <v>220.1589472416603</v>
+        <v>237.0274053429224</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.204135593974027</v>
+        <v>346.738524770901</v>
       </c>
       <c r="G16" t="n">
-        <v>-143.9135948067311</v>
+        <v>12.45939554309132</v>
       </c>
       <c r="H16" t="n">
-        <v>0.006533660572314824</v>
+        <v>0.8706120690520608</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1438121466237398</v>
+        <v>0.04571596649227151</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05370687630395001</v>
+        <v>0.886451816664215</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1904638673064294</v>
+        <v>0.0707727276329307</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09081039300041477</v>
+        <v>0.4649801025643017</v>
       </c>
     </row>
     <row r="17">
@@ -1069,34 +1069,34 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D17" t="n">
-        <v>292.2393974133499</v>
+        <v>473.8018015594213</v>
       </c>
       <c r="E17" t="n">
-        <v>216.6956489820461</v>
+        <v>237.8444803026007</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.13928597185888</v>
+        <v>342.4526148556619</v>
       </c>
       <c r="G17" t="n">
-        <v>-138.1516830463438</v>
+        <v>18.91237741223745</v>
       </c>
       <c r="H17" t="n">
-        <v>0.006287043811375693</v>
+        <v>0.842572965314934</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1195917504436671</v>
+        <v>0.06320944348101823</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08369687208070482</v>
+        <v>0.8603403451796841</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1613747139506298</v>
+        <v>0.1090854546285149</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08280486242357003</v>
+        <v>0.4634984362333505</v>
       </c>
     </row>
     <row r="18">
@@ -1107,34 +1107,34 @@
         <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D18" t="n">
-        <v>292.3891402613979</v>
+        <v>467.9061750310885</v>
       </c>
       <c r="E18" t="n">
-        <v>209.6008870464008</v>
+        <v>240.1935667808787</v>
       </c>
       <c r="F18" t="n">
-        <v>-18.45728098321847</v>
+        <v>334.6255007784296</v>
       </c>
       <c r="G18" t="n">
-        <v>-125.7614693990233</v>
+        <v>32.79929951322056</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01251738940723575</v>
+        <v>0.7920451393693922</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06997490199360872</v>
+        <v>0.1135031035247806</v>
       </c>
       <c r="J18" t="n">
-        <v>0.139467711415935</v>
+        <v>0.8126544464847231</v>
       </c>
       <c r="K18" t="n">
-        <v>0.09882241535836492</v>
+        <v>0.1915350672344019</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06721245159599815</v>
+        <v>0.4692143332512451</v>
       </c>
     </row>
     <row r="19">
@@ -1145,34 +1145,34 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D19" t="n">
-        <v>292.5196297690709</v>
+        <v>466.9406448540248</v>
       </c>
       <c r="E19" t="n">
-        <v>204.7068323741094</v>
+        <v>242.4507115939257</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.28869274537767</v>
+        <v>333.1645750002364</v>
       </c>
       <c r="G19" t="n">
-        <v>-116.6230470542762</v>
+        <v>43.07258839838555</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01794666192365193</v>
+        <v>0.7837701679991077</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03574858528502776</v>
+        <v>0.1618283035319533</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1534250003981607</v>
+        <v>0.803753904347178</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05268686520225672</v>
+        <v>0.2525297702082346</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05225039333629614</v>
+        <v>0.4912467696029224</v>
       </c>
     </row>
     <row r="20">
@@ -1183,34 +1183,34 @@
         <v>60</v>
       </c>
       <c r="C20" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D20" t="n">
-        <v>292.4614658329668</v>
+        <v>474.1397708749843</v>
       </c>
       <c r="E20" t="n">
-        <v>204.5865754070507</v>
+        <v>242.5743968754382</v>
       </c>
       <c r="F20" t="n">
-        <v>-12.68220238169772</v>
+        <v>342.3688361547703</v>
       </c>
       <c r="G20" t="n">
-        <v>-116.3521437874698</v>
+        <v>43.44244709464915</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01552663700848462</v>
+        <v>0.8454694945760109</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03490757444298139</v>
+        <v>0.1644763905897651</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09545552223928495</v>
+        <v>0.8598299319412812</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05131920339131174</v>
+        <v>0.254725700019326</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04127385808892145</v>
+        <v>0.5224079003820267</v>
       </c>
     </row>
     <row r="21">
@@ -1221,34 +1221,34 @@
         <v>75</v>
       </c>
       <c r="C21" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D21" t="n">
-        <v>292.6969715645987</v>
+        <v>484.6861269920848</v>
       </c>
       <c r="E21" t="n">
-        <v>207.4732538302589</v>
+        <v>241.2441702900717</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.166484353139172</v>
+        <v>355.8237808634494</v>
       </c>
       <c r="G21" t="n">
-        <v>-121.7677276397646</v>
+        <v>37.44402950373918</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02532531599048856</v>
+        <v>0.935855892643061</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05509540979919988</v>
+        <v>0.1359963987783766</v>
       </c>
       <c r="J21" t="n">
-        <v>0.007693606714115307</v>
+        <v>0.9418028179875836</v>
       </c>
       <c r="K21" t="n">
-        <v>0.07865991177800304</v>
+        <v>0.2191118179061793</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04119916167858254</v>
+        <v>0.5507698697894396</v>
       </c>
     </row>
     <row r="22">
@@ -1259,34 +1259,34 @@
         <v>90</v>
       </c>
       <c r="C22" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D22" t="n">
-        <v>292.963922920278</v>
+        <v>489.6889858594613</v>
       </c>
       <c r="E22" t="n">
-        <v>209.2106852051356</v>
+        <v>240.5227343174773</v>
       </c>
       <c r="F22" t="n">
-        <v>4.294301096097895</v>
+        <v>362.1548882736342</v>
       </c>
       <c r="G22" t="n">
-        <v>-124.9444755208731</v>
+        <v>33.91468195246738</v>
       </c>
       <c r="H22" t="n">
-        <v>0.03643235198484349</v>
+        <v>0.9787323504488766</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06724604571927491</v>
+        <v>0.1205505410440977</v>
       </c>
       <c r="J22" t="n">
-        <v>0.03153086880172436</v>
+        <v>0.9803744477875347</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0946978016536484</v>
+        <v>0.1981573302063242</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05559757764393492</v>
+        <v>0.5628495934966345</v>
       </c>
     </row>
     <row r="23">
@@ -1297,34 +1297,34 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D23" t="n">
-        <v>292.0882918556192</v>
+        <v>469.6024195334531</v>
       </c>
       <c r="E23" t="n">
-        <v>232.3089378209159</v>
+        <v>235.458906412013</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.26745874972438</v>
+        <v>337.3818716619319</v>
       </c>
       <c r="G23" t="n">
-        <v>-163.1016414334063</v>
+        <v>-9.244920365235085</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.8065826183912868</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2287824735647707</v>
+        <v>0.0121345923114497</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1075368475297677</v>
+        <v>0.8294473565432042</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2873351930283758</v>
+        <v>0.05168770424054602</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1420728312812808</v>
+        <v>0.4197615803648706</v>
       </c>
     </row>
     <row r="24">
@@ -1335,34 +1335,34 @@
         <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D24" t="n">
-        <v>292.2459408414853</v>
+        <v>464.7391666746348</v>
       </c>
       <c r="E24" t="n">
-        <v>226.6283058664807</v>
+        <v>235.8664656423721</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.18523335374839</v>
+        <v>330.9339097610336</v>
       </c>
       <c r="G24" t="n">
-        <v>-154.3659439543518</v>
+        <v>0.5392018096106476</v>
       </c>
       <c r="H24" t="n">
-        <v>0.006559296003694665</v>
+        <v>0.7649026386980993</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1890552695598442</v>
+        <v>0.02086038660166509</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1526365307286241</v>
+        <v>0.7901638026098842</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2432328092700712</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1311830785209622</v>
+        <v>0.3936149755349022</v>
       </c>
     </row>
     <row r="25">
@@ -1373,34 +1373,34 @@
         <v>30</v>
       </c>
       <c r="C25" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D25" t="n">
-        <v>292.8875804437707</v>
+        <v>456.0081377746115</v>
       </c>
       <c r="E25" t="n">
-        <v>215.1580411479885</v>
+        <v>238.1216443161823</v>
       </c>
       <c r="F25" t="n">
-        <v>-31.20009316742418</v>
+        <v>319.1481003648897</v>
       </c>
       <c r="G25" t="n">
-        <v>-135.6347399787646</v>
+        <v>21.53475904233506</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03325597315617021</v>
+        <v>0.6900743051078061</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1088385700593108</v>
+        <v>0.0691434918033506</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2365813784656091</v>
+        <v>0.7183599541726358</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1486678649176437</v>
+        <v>0.1246550925896176</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1115730549690358</v>
+        <v>0.3935751067640944</v>
       </c>
     </row>
     <row r="26">
@@ -1411,34 +1411,34 @@
         <v>45</v>
       </c>
       <c r="C26" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D26" t="n">
-        <v>293.2054884431762</v>
+        <v>454.5884609279651</v>
       </c>
       <c r="E26" t="n">
-        <v>207.4288946518311</v>
+        <v>240.9820666587534</v>
       </c>
       <c r="F26" t="n">
-        <v>-33.95850825649543</v>
+        <v>316.9470392907011</v>
       </c>
       <c r="G26" t="n">
-        <v>-121.8653602770455</v>
+        <v>37.01542388244143</v>
       </c>
       <c r="H26" t="n">
-        <v>0.04648316049636832</v>
+        <v>0.6779071190994095</v>
       </c>
       <c r="I26" t="n">
-        <v>0.05478518619291333</v>
+        <v>0.1303847914358413</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2576034103901549</v>
+        <v>0.7049502128082562</v>
       </c>
       <c r="K26" t="n">
-        <v>0.07915281255061102</v>
+        <v>0.2165670950957731</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0898821527198882</v>
+        <v>0.4230168548290885</v>
       </c>
     </row>
     <row r="27">
@@ -1449,34 +1449,34 @@
         <v>60</v>
       </c>
       <c r="C27" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D27" t="n">
-        <v>292.6454535612152</v>
+        <v>465.2527614326324</v>
       </c>
       <c r="E27" t="n">
-        <v>207.239678229605</v>
+        <v>241.1550615216369</v>
       </c>
       <c r="F27" t="n">
-        <v>-22.50595757330057</v>
+        <v>330.8084618032313</v>
       </c>
       <c r="G27" t="n">
-        <v>-121.4577487269437</v>
+        <v>37.57196771816093</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02318180817243901</v>
+        <v>0.7693043467123254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.05346191098917652</v>
+        <v>0.1340885907227697</v>
       </c>
       <c r="J27" t="n">
-        <v>0.170322896651136</v>
+        <v>0.7893995236498197</v>
       </c>
       <c r="K27" t="n">
-        <v>0.07709497560627883</v>
+        <v>0.2198714143192545</v>
       </c>
       <c r="L27" t="n">
-        <v>0.06678421843010764</v>
+        <v>0.4693428021398774</v>
       </c>
     </row>
     <row r="28">
@@ -1487,34 +1487,34 @@
         <v>75</v>
       </c>
       <c r="C28" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D28" t="n">
-        <v>292.5803337812836</v>
+        <v>480.9649290114236</v>
       </c>
       <c r="E28" t="n">
-        <v>211.7693284192273</v>
+        <v>239.4187095488446</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.194461047615595</v>
+        <v>351.0378637829094</v>
       </c>
       <c r="G28" t="n">
-        <v>-129.6124035830856</v>
+        <v>28.53919561791757</v>
       </c>
       <c r="H28" t="n">
-        <v>0.02047237169924833</v>
+        <v>0.9039637700718376</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08513978390850635</v>
+        <v>0.09691350302657463</v>
       </c>
       <c r="J28" t="n">
-        <v>0.03839103691528192</v>
+        <v>0.9126451035588431</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1182639513800391</v>
+        <v>0.1662419235648125</v>
       </c>
       <c r="L28" t="n">
-        <v>0.06131321658513841</v>
+        <v>0.51344026222008</v>
       </c>
     </row>
     <row r="29">
@@ -1525,34 +1525,34 @@
         <v>90</v>
       </c>
       <c r="C29" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D29" t="n">
-        <v>292.9052472438822</v>
+        <v>488.4507446879326</v>
       </c>
       <c r="E29" t="n">
-        <v>214.5265971981574</v>
+        <v>238.5425959497798</v>
       </c>
       <c r="F29" t="n">
-        <v>3.003581594836065</v>
+        <v>360.5431267642628</v>
       </c>
       <c r="G29" t="n">
-        <v>-134.4021369981503</v>
+        <v>23.21763239485585</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03399103510872994</v>
+        <v>0.9681201391609109</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1044225996507663</v>
+        <v>0.07815601584228687</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02169422504616266</v>
+        <v>0.970554954255443</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1424450384286284</v>
+        <v>0.1346466699147534</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07349442216563058</v>
+        <v>0.5329589890294321</v>
       </c>
     </row>
     <row r="30">
@@ -1563,34 +1563,34 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D30" t="n">
-        <v>292.3212915510654</v>
+        <v>454.8357160378376</v>
       </c>
       <c r="E30" t="n">
-        <v>259.7441885668012</v>
+        <v>238.4898711121679</v>
       </c>
       <c r="F30" t="n">
-        <v>-28.44302291405067</v>
+        <v>318.5918865489093</v>
       </c>
       <c r="G30" t="n">
-        <v>-202.1660312234017</v>
+        <v>-53.43669932249846</v>
       </c>
       <c r="H30" t="n">
-        <v>0.009694410419487742</v>
+        <v>0.6800261921268045</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4206494721752227</v>
+        <v>0.07702718338624986</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2155695956073055</v>
+        <v>0.7149712779096017</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4845527264804206</v>
+        <v>0.314063702960479</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2601350145461912</v>
+        <v>0.4238569553160316</v>
       </c>
     </row>
     <row r="31">
@@ -1601,34 +1601,34 @@
         <v>15</v>
       </c>
       <c r="C31" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D31" t="n">
-        <v>293.1442712030078</v>
+        <v>446.8959905867329</v>
       </c>
       <c r="E31" t="n">
-        <v>248.8769347169675</v>
+        <v>236.2875450107761</v>
       </c>
       <c r="F31" t="n">
-        <v>-38.35674270884249</v>
+        <v>307.7807471665274</v>
       </c>
       <c r="G31" t="n">
-        <v>-187.2814866438569</v>
+        <v>-36.76327409909055</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0439360968626398</v>
+        <v>0.6119796386823395</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3446498978094524</v>
+        <v>0.0298756454275024</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2911225951695594</v>
+        <v>0.6491055076808301</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4094077367771222</v>
+        <v>0.2150700281571988</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2462837202151443</v>
+        <v>0.3579810173429521</v>
       </c>
     </row>
     <row r="32">
@@ -1639,34 +1639,34 @@
         <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D32" t="n">
-        <v>295.6116812136619</v>
+        <v>432.7790787442274</v>
       </c>
       <c r="E32" t="n">
-        <v>227.2866742859935</v>
+        <v>235.5517437518293</v>
       </c>
       <c r="F32" t="n">
-        <v>-56.84310046285535</v>
+        <v>287.9845800216917</v>
       </c>
       <c r="G32" t="n">
-        <v>-155.5584561288621</v>
+        <v>-1.199425834431561</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1465975414221747</v>
+        <v>0.4909921811087035</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1936595348462026</v>
+        <v>0.01412222863359668</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4320081364403906</v>
+        <v>0.5284993670647021</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2492532363376067</v>
+        <v>0.003919890576453232</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2269625875524587</v>
+        <v>0.2571080128542926</v>
       </c>
     </row>
     <row r="33">
@@ -1677,34 +1677,34 @@
         <v>45</v>
       </c>
       <c r="C33" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D33" t="n">
-        <v>296.5481797257702</v>
+        <v>430.5243764700355</v>
       </c>
       <c r="E33" t="n">
-        <v>213.1907260343662</v>
+        <v>238.475893766432</v>
       </c>
       <c r="F33" t="n">
-        <v>-61.47883102087715</v>
+        <v>284.2832474092314</v>
       </c>
       <c r="G33" t="n">
-        <v>-132.3992831994726</v>
+        <v>24.84256904874991</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1855624032269645</v>
+        <v>0.4716685004919117</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09508025417337733</v>
+        <v>0.07672793008874285</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4673372920016511</v>
+        <v>0.5059493735099194</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1323335817243581</v>
+        <v>0.1442942647272271</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1934926980877821</v>
+        <v>0.2911727498997426</v>
       </c>
     </row>
     <row r="34">
@@ -1715,34 +1715,34 @@
         <v>60</v>
       </c>
       <c r="C34" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D34" t="n">
-        <v>294.0311631862959</v>
+        <v>447.7744987366709</v>
       </c>
       <c r="E34" t="n">
-        <v>212.847032227177</v>
+        <v>238.7205883915213</v>
       </c>
       <c r="F34" t="n">
-        <v>-42.24604653803784</v>
+        <v>307.5724426418802</v>
       </c>
       <c r="G34" t="n">
-        <v>-131.7156827547662</v>
+        <v>25.77607915564248</v>
       </c>
       <c r="H34" t="n">
-        <v>0.08083698150665279</v>
+        <v>0.6195087972337647</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09267664941549876</v>
+        <v>0.08196681269377995</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3207631918968384</v>
+        <v>0.64783643349052</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1288824080519553</v>
+        <v>0.1498367129470183</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1327788102988494</v>
+        <v>0.3667707277154379</v>
       </c>
     </row>
     <row r="35">
@@ -1753,34 +1753,34 @@
         <v>75</v>
       </c>
       <c r="C35" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D35" t="n">
-        <v>292.5167370170171</v>
+        <v>473.5670697765982</v>
       </c>
       <c r="E35" t="n">
-        <v>221.0272333374856</v>
+        <v>236.7300995709382</v>
       </c>
       <c r="F35" t="n">
-        <v>-13.2658127395045</v>
+        <v>341.4464882481848</v>
       </c>
       <c r="G35" t="n">
-        <v>-145.4128999420187</v>
+        <v>10.60218554451877</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01782630328714296</v>
+        <v>0.8405612220999634</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1498844602571838</v>
+        <v>0.03935068553582772</v>
       </c>
       <c r="J35" t="n">
-        <v>0.09990324862459865</v>
+        <v>0.8542106208643049</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1980331461883723</v>
+        <v>0.05974607652935414</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1055596536502708</v>
+        <v>0.4456300854442068</v>
       </c>
     </row>
     <row r="36">
@@ -1791,34 +1791,34 @@
         <v>90</v>
       </c>
       <c r="C36" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D36" t="n">
-        <v>292.8051818350872</v>
+        <v>485.979403909266</v>
       </c>
       <c r="E36" t="n">
-        <v>226.0915652776253</v>
+        <v>235.9945080642359</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4205678889714593</v>
+        <v>357.3173934991935</v>
       </c>
       <c r="G36" t="n">
-        <v>-153.4797776905987</v>
+        <v>1.638909092565612</v>
       </c>
       <c r="H36" t="n">
-        <v>0.02982761704161649</v>
+        <v>0.9469397818033872</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1853016021787816</v>
+        <v>0.02360175951234467</v>
       </c>
       <c r="J36" t="n">
-        <v>0.002008936634944034</v>
+        <v>0.9509025014896785</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2387589770739114</v>
+        <v>0.00652919623226593</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1118377253582753</v>
+        <v>0.483085796725568</v>
       </c>
     </row>
     <row r="37">
@@ -1829,34 +1829,34 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D37" t="n">
-        <v>294.0525327822085</v>
+        <v>433.1928963997794</v>
       </c>
       <c r="E37" t="n">
-        <v>307.3378355796964</v>
+        <v>258.6305620178532</v>
       </c>
       <c r="F37" t="n">
-        <v>-49.83043404640308</v>
+        <v>290.2119584177983</v>
       </c>
       <c r="G37" t="n">
-        <v>-262.6147592362543</v>
+        <v>-121.8326790897366</v>
       </c>
       <c r="H37" t="n">
-        <v>0.08172610555841546</v>
+        <v>0.4945387603182989</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7534931662194283</v>
+        <v>0.5082369625168979</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3785642229891757</v>
+        <v>0.5420694440437825</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7897296178409889</v>
+        <v>0.7201451942082515</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4731220640643086</v>
+        <v>0.544627680653738</v>
       </c>
     </row>
     <row r="38">
@@ -1867,34 +1867,34 @@
         <v>15</v>
       </c>
       <c r="C38" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D38" t="n">
-        <v>296.7183484292779</v>
+        <v>420.9717337444823</v>
       </c>
       <c r="E38" t="n">
-        <v>287.2643613257428</v>
+        <v>248.279581823475</v>
       </c>
       <c r="F38" t="n">
-        <v>-65.8166759136772</v>
+        <v>272.7556184644545</v>
       </c>
       <c r="G38" t="n">
-        <v>-237.949399894441</v>
+        <v>-94.19599094385848</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1926426066976002</v>
+        <v>0.3897986149696369</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6131103684654148</v>
+        <v>0.2866237167595947</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5003962446522014</v>
+        <v>0.4357184632881395</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6652059440487881</v>
+        <v>0.5560602936977166</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4628513565045032</v>
+        <v>0.3907705700740533</v>
       </c>
     </row>
     <row r="39">
@@ -1905,34 +1905,34 @@
         <v>30</v>
       </c>
       <c r="C39" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D39" t="n">
-        <v>303.982876524206</v>
+        <v>399.7152063371141</v>
       </c>
       <c r="E39" t="n">
-        <v>247.7534583469604</v>
+        <v>235.8865980563247</v>
       </c>
       <c r="F39" t="n">
-        <v>-95.71110724286508</v>
+        <v>240.7029797455988</v>
       </c>
       <c r="G39" t="n">
-        <v>-185.9033656332317</v>
+        <v>-35.83273144832043</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4948975805561746</v>
+        <v>0.2076218587106461</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3367929242712985</v>
+        <v>0.02129141917222209</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7282233371946518</v>
+        <v>0.2404410126502914</v>
       </c>
       <c r="K39" t="n">
-        <v>0.4024502589315693</v>
+        <v>0.2095451983560854</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4656757676301946</v>
+        <v>0.1513021277953522</v>
       </c>
     </row>
     <row r="40">
@@ -1943,34 +1943,34 @@
         <v>45</v>
       </c>
       <c r="C40" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D40" t="n">
-        <v>306.4270924859435</v>
+        <v>396.4526465924228</v>
       </c>
       <c r="E40" t="n">
-        <v>222.5842867390855</v>
+        <v>235.8495980934073</v>
       </c>
       <c r="F40" t="n">
-        <v>-103.2233491832628</v>
+        <v>234.6991463093196</v>
       </c>
       <c r="G40" t="n">
-        <v>-148.3257665825373</v>
+        <v>6.434095208743902</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5965939911097354</v>
+        <v>0.1796604452587474</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1607736322063768</v>
+        <v>0.02049925439931684</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7854745429764196</v>
+        <v>0.2038632663444566</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2127388251252787</v>
+        <v>0.03499923694949864</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4188247691223204</v>
+        <v>0.1065303171016806</v>
       </c>
     </row>
     <row r="41">
@@ -1981,34 +1981,34 @@
         <v>60</v>
       </c>
       <c r="C41" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D41" t="n">
-        <v>298.6583419871952</v>
+        <v>422.4323577161172</v>
       </c>
       <c r="E41" t="n">
-        <v>221.9707352958798</v>
+        <v>236.1295539947225</v>
       </c>
       <c r="F41" t="n">
-        <v>-72.09208339177469</v>
+        <v>272.4243691411132</v>
       </c>
       <c r="G41" t="n">
-        <v>-147.2215673547759</v>
+        <v>7.942308964207161</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2733598528107355</v>
+        <v>0.4023167338592885</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1564827921119538</v>
+        <v>0.02649307670351315</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5482214675009193</v>
+        <v>0.4337003603807633</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2071642481432895</v>
+        <v>0.04395382306732616</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2691785009149313</v>
+        <v>0.2225456340956155</v>
       </c>
     </row>
     <row r="42">
@@ -2019,34 +2019,34 @@
         <v>75</v>
       </c>
       <c r="C42" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D42" t="n">
-        <v>292.8488567011248</v>
+        <v>462.5897499467564</v>
       </c>
       <c r="E42" t="n">
-        <v>236.4404791630438</v>
+        <v>235.249597437852</v>
       </c>
       <c r="F42" t="n">
-        <v>-25.41163344711041</v>
+        <v>327.0101686575713</v>
       </c>
       <c r="G42" t="n">
-        <v>-169.3995726774452</v>
+        <v>-16.63101599367908</v>
       </c>
       <c r="H42" t="n">
-        <v>0.03164479571034018</v>
+        <v>0.7464812964050034</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2576761929731116</v>
+        <v>0.007653312253050832</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1924672110524103</v>
+        <v>0.7662588078801894</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3191304539418847</v>
+        <v>0.09554052625588161</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1817066070601997</v>
+        <v>0.39501142524203</v>
       </c>
     </row>
     <row r="43">
@@ -2057,34 +2057,34 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D43" t="n">
-        <v>292.6984470644013</v>
+        <v>482.285546009132</v>
       </c>
       <c r="E43" t="n">
-        <v>245.5398388583232</v>
+        <v>235.925838347276</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.4578990963323</v>
+        <v>352.4732527245187</v>
       </c>
       <c r="G43" t="n">
-        <v>-182.5163765807535</v>
+        <v>-31.20714526786165</v>
       </c>
       <c r="H43" t="n">
-        <v>0.025386707060689</v>
+        <v>0.9152819744187812</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3213120915541377</v>
+        <v>0.02213154909990617</v>
       </c>
       <c r="J43" t="n">
-        <v>0.025156603517834</v>
+        <v>0.9213900651094292</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3853509613270309</v>
+        <v>0.1820821085597531</v>
       </c>
       <c r="L43" t="n">
-        <v>0.1839841936790864</v>
+        <v>0.4963832034510929</v>
       </c>
     </row>
     <row r="44">
@@ -2095,34 +2095,34 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D44" t="n">
-        <v>296.1310283059035</v>
+        <v>419.1633675821897</v>
       </c>
       <c r="E44" t="n">
-        <v>342.5860900701685</v>
+        <v>281.5995386416121</v>
       </c>
       <c r="F44" t="n">
-        <v>-64.17282961287049</v>
+        <v>271.159435205635</v>
       </c>
       <c r="G44" t="n">
-        <v>-304.264626903564</v>
+        <v>-168.9683994986677</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1682059982603545</v>
+        <v>0.374300209455819</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4878684022866638</v>
+        <v>0.4259938786676005</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6373800664678955</v>
+        <v>0.6957657162632064</v>
       </c>
     </row>
     <row r="45">
@@ -2133,34 +2133,34 @@
         <v>15</v>
       </c>
       <c r="C45" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D45" t="n">
-        <v>300.5760967420781</v>
+        <v>404.3716906562211</v>
       </c>
       <c r="E45" t="n">
-        <v>315.6348000816515</v>
+        <v>263.5862003420096</v>
       </c>
       <c r="F45" t="n">
-        <v>-84.26132524788912</v>
+        <v>249.2037736628625</v>
       </c>
       <c r="G45" t="n">
-        <v>-272.6576174900079</v>
+        <v>-133.5471343165793</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3531518098008907</v>
+        <v>0.2475297511226362</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8115175557652874</v>
+        <v>0.6143365852764945</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6409639237796405</v>
+        <v>0.292231237446493</v>
       </c>
       <c r="K45" t="n">
-        <v>0.840431234947038</v>
+        <v>0.7896964085319648</v>
       </c>
       <c r="L45" t="n">
-        <v>0.6351223149765058</v>
+        <v>0.4676100531294532</v>
       </c>
     </row>
     <row r="46">
@@ -2171,34 +2171,34 @@
         <v>30</v>
       </c>
       <c r="C46" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D46" t="n">
-        <v>312.3267799794897</v>
+        <v>379.201059453527</v>
       </c>
       <c r="E46" t="n">
-        <v>262.7325265475453</v>
+        <v>239.0183440460194</v>
       </c>
       <c r="F46" t="n">
-        <v>-121.9002587635533</v>
+        <v>208.8125336293223</v>
       </c>
       <c r="G46" t="n">
-        <v>-206.4530910589449</v>
+        <v>-59.29223850225634</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8420620883947525</v>
+        <v>0.03180759398850854</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4415482583576298</v>
+        <v>0.08834172558094219</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9278122901140041</v>
+        <v>0.04615170399419335</v>
       </c>
       <c r="K46" t="n">
-        <v>0.506196053589134</v>
+        <v>0.3488292855322609</v>
       </c>
       <c r="L46" t="n">
-        <v>0.6668715062013172</v>
+        <v>0.1058799381108926</v>
       </c>
     </row>
     <row r="47">
@@ -2209,34 +2209,34 @@
         <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D47" t="n">
-        <v>316.1227287490456</v>
+        <v>375.4897243344739</v>
       </c>
       <c r="E47" t="n">
-        <v>229.3144502390984</v>
+        <v>234.8921310631233</v>
       </c>
       <c r="F47" t="n">
-        <v>-131.3724006054905</v>
+        <v>201.2372406830371</v>
       </c>
       <c r="G47" t="n">
-        <v>-159.0290480350785</v>
+        <v>-5.939993924294662</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2078406804672263</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.266774605007185</v>
+        <v>0.0320656524449793</v>
       </c>
       <c r="L47" t="n">
-        <v>0.613742660990273</v>
+        <v>0.00534427540749655</v>
       </c>
     </row>
     <row r="48">
@@ -2247,34 +2247,34 @@
         <v>60</v>
       </c>
       <c r="C48" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D48" t="n">
-        <v>303.4199887262319</v>
+        <v>406.2433546054451</v>
       </c>
       <c r="E48" t="n">
-        <v>228.4979866763785</v>
+        <v>235.1441464532179</v>
       </c>
       <c r="F48" t="n">
-        <v>-92.15029016563426</v>
+        <v>248.7915680257999</v>
       </c>
       <c r="G48" t="n">
-        <v>-157.63988953652</v>
+        <v>-4.042260293672699</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4714775270525265</v>
+        <v>0.2635706434350051</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2021307850226814</v>
+        <v>0.005395619306661123</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7010861559300954</v>
+        <v>0.2897199164083044</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2597614041321053</v>
+        <v>0.02079840391170876</v>
       </c>
       <c r="L48" t="n">
-        <v>0.384677364035436</v>
+        <v>0.1414084743005576</v>
       </c>
     </row>
     <row r="49">
@@ -2285,34 +2285,34 @@
         <v>75</v>
       </c>
       <c r="C49" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D49" t="n">
-        <v>293.3571124200595</v>
+        <v>455.3579027609474</v>
       </c>
       <c r="E49" t="n">
-        <v>247.6342421416871</v>
+        <v>236.0493000106545</v>
       </c>
       <c r="F49" t="n">
-        <v>-33.53494369306436</v>
+        <v>317.3528003967417</v>
       </c>
       <c r="G49" t="n">
-        <v>-185.5878909919601</v>
+        <v>-35.0125605407154</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05279177415583014</v>
+        <v>0.6845015366435511</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3359591919426467</v>
+        <v>0.02477484852026214</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2543754017377108</v>
+        <v>0.7074222711947938</v>
       </c>
       <c r="K49" t="n">
-        <v>0.400857577439481</v>
+        <v>0.204675669088843</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2387891518956909</v>
+        <v>0.3884417851018772</v>
       </c>
     </row>
     <row r="50">
@@ -2323,34 +2323,34 @@
         <v>90</v>
       </c>
       <c r="C50" t="n">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="D50" t="n">
-        <v>292.6563074006577</v>
+        <v>479.8319804585219</v>
       </c>
       <c r="E50" t="n">
-        <v>259.7441885668013</v>
+        <v>238.4898711121679</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.046182254857579</v>
+        <v>349.2401196984882</v>
       </c>
       <c r="G50" t="n">
-        <v>-202.1660312234017</v>
+        <v>-53.43669932249845</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0236334035017012</v>
+        <v>0.8942539577200604</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4206494721752231</v>
+        <v>0.07702718338624986</v>
       </c>
       <c r="J50" t="n">
-        <v>0.04488205071534132</v>
+        <v>0.9016925300504868</v>
       </c>
       <c r="K50" t="n">
-        <v>0.4845527264804209</v>
+        <v>0.314063702960479</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2363334214249352</v>
+        <v>0.526386419203931</v>
       </c>
     </row>
   </sheetData>
@@ -2406,25 +2406,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02072069904797467</v>
+        <v>0.00534427540749655</v>
       </c>
       <c r="D2" t="n">
-        <v>292.6137025687393</v>
+        <v>375.4897243344739</v>
       </c>
       <c r="E2" t="n">
-        <v>202.0374786696764</v>
+        <v>234.8921310631233</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.88892143358464</v>
+        <v>201.2372406830371</v>
       </c>
       <c r="G2" t="n">
-        <v>-111.2619255046742</v>
+        <v>-5.939993924294662</v>
       </c>
     </row>
   </sheetData>
